--- a/projects/paper-01/03-screen/数据_3_第二轮人工摘要筛选.xlsx
+++ b/projects/paper-01/03-screen/数据_3_第二轮人工摘要筛选.xlsx
@@ -37,7 +37,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +52,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -103,6 +108,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3569,31 +3583,43 @@
       </c>
     </row>
     <row r="100" ht="80" customHeight="1">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="8" t="n">
         <v>620</v>
       </c>
-      <c r="B100" s="2" t="inlineStr"/>
-      <c r="C100" s="2" t="inlineStr"/>
-      <c r="D100" s="3" t="inlineStr"/>
-      <c r="E100" s="4" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>E1-非老年人群</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>MCI患者（第一轮漏网）</t>
+        </is>
+      </c>
+      <c r="E100" s="10" t="inlineStr">
         <is>
           <t>Development and effectiveness of virtual interactive working memory training for older people with mild cognitive impairment: a single-blind randomised controlled trial.</t>
         </is>
       </c>
-      <c r="F100" s="3" t="inlineStr">
+      <c r="F100" s="9" t="inlineStr">
         <is>
           <t>Yang HL; Chu H; Kao CC et al.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="n">
+      <c r="G100" s="8" t="n">
         <v>2019</v>
       </c>
-      <c r="H100" s="3" t="inlineStr">
+      <c r="H100" s="9" t="inlineStr">
         <is>
           <t>Age and ageing</t>
         </is>
       </c>
-      <c r="I100" s="4" t="inlineStr">
+      <c r="I100" s="10" t="inlineStr">
         <is>
           <t>BACKGROUND: memory training is a potential intervention for retaining memory and reducing dementia risk in older adults with mild cognitive impairment (MCI). OBJECTIVE: this study examined the effect of virtual interactive working memory training (VIMT) in older adults with MCI. DESIGN: single-blind, two-arm parallel-group, randomised controlled design. SETTING: retirement homes, institutions, and communities. SUBJECTS: a total of 66 older adults with MCI were recruited (mean age: 78.5 ± 7.6 years). METHODS: participants were randomly assigned to the experimental group (VIMT, n = 33) or active control group (n = 33). The VIMT program used the CogniPlus (includes four training modules). Both groups attended 45 min sessions 3 times per week, a total of 36 sessions. The primary outcome was working memory; secondary outcomes were immediate memory, delayed memory, subjective memory complaints and global cognitive function. All variables were measured at pre-test, post-test, and 3-month follow-up. RESULTS: between group, the effect of working memory adjusted mean difference by 1.75 (95% CI: 0.56 to 2.94; P &lt; 0.01) at post-test. The results were analysed by a generalised estimating equation, which indicated that VIMT group significantly improved working memory at post-test (P = 0.01) relative to the active control group. CONCLUSIONS: the applied VIMT program can enable older adults with MCI to maintain their working memory and reduce the rate of cognitive deterioration. TRIAL REGISTRATION: This trial was registered on ClinicalTrials.gov (no.: NCT02462135).</t>
         </is>
@@ -5150,31 +5176,43 @@
       </c>
     </row>
     <row r="151" ht="80" customHeight="1">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="8" t="n">
         <v>1039</v>
       </c>
-      <c r="B151" s="2" t="inlineStr"/>
-      <c r="C151" s="2" t="inlineStr"/>
-      <c r="D151" s="3" t="inlineStr"/>
-      <c r="E151" s="4" t="inlineStr">
+      <c r="B151" s="8" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C151" s="8" t="inlineStr">
+        <is>
+          <t>E1-非老年人群</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>帕金森病患者（第一轮漏网）</t>
+        </is>
+      </c>
+      <c r="E151" s="10" t="inlineStr">
         <is>
           <t>Effects of working memory training in patients with Parkinson's disease without cognitive impairment: A randomized controlled trial.</t>
         </is>
       </c>
-      <c r="F151" s="3" t="inlineStr">
+      <c r="F151" s="9" t="inlineStr">
         <is>
           <t>Ophey A; Giehl K; Rehberg S et al.</t>
         </is>
       </c>
-      <c r="G151" s="2" t="n">
+      <c r="G151" s="8" t="n">
         <v>2020</v>
       </c>
-      <c r="H151" s="3" t="inlineStr">
+      <c r="H151" s="9" t="inlineStr">
         <is>
           <t>Parkinsonism &amp; related disorders</t>
         </is>
       </c>
-      <c r="I151" s="4" t="inlineStr">
+      <c r="I151" s="10" t="inlineStr">
         <is>
           <t>OBJECTIVE: To determine the feasibility and evaluate effects of a computerized working memory (WM) training (WMT) in patients with Parkinson's Disease (PD) on cognitive and clinical outcomes. METHODS: 76 patients with PD without cognitive impairment were randomized to either the WMT group (n = 37), who participated in a 5-week adaptive WMT, or a passive waiting-list control group (CG, n = 39). Patients underwent clinical and neuropsychological examination at baseline, after training, and at 3-months follow-up, with verbal WM and non-verbal WM as primary outcomes. Outcome assessors were blinded for group allocation. RESULTS: All WMT participants completed the training successfully and reported high levels of motivation for and satisfaction with the training. Repeated-measures, linear mixed-effects models revealed positive training effects for the WMT group compared to the CG in verbal working memory with a small relative effect size 0.39 [95%CI 0.05; 0.76] for the 3-months follow-up only. No other reliable training effects in cognitive and clinical variables were found for either point of time. CONCLUSIONS: In this randomized controlled trial, WMT was feasible and yielded some evidence for 3-months follow-up training gains in patients with PD. WMT might be an effective intervention to prevent cognitive decline in this patient group, however, more longitudinal studies with longer follow-up periods and more sensitive assessment tools will have to proof this concept. TRIAL REGISTRATION: German Clinical Trials Register (DRKS00009379).</t>
         </is>
@@ -5677,31 +5715,43 @@
       </c>
     </row>
     <row r="168" ht="80" customHeight="1">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="8" t="n">
         <v>1260</v>
       </c>
-      <c r="B168" s="2" t="inlineStr"/>
-      <c r="C168" s="2" t="inlineStr"/>
-      <c r="D168" s="3" t="inlineStr"/>
-      <c r="E168" s="4" t="inlineStr">
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C168" s="8" t="inlineStr">
+        <is>
+          <t>E1-非老年人群</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="inlineStr">
+        <is>
+          <t>MCI患者（第一轮漏网）</t>
+        </is>
+      </c>
+      <c r="E168" s="10" t="inlineStr">
         <is>
           <t>Individualised computerised cognitive training (iCCT) for community-dwelling people with mild cognitive impairment (MCI): results on cognition in the 6-month intervention period of a randomised controlled trial (MCI-CCT study).</t>
         </is>
       </c>
-      <c r="F168" s="3" t="inlineStr">
+      <c r="F168" s="9" t="inlineStr">
         <is>
           <t>Graessel E; Jank M; Scheerbaum P et al.</t>
         </is>
       </c>
-      <c r="G168" s="2" t="n">
+      <c r="G168" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="H168" s="3" t="inlineStr">
+      <c r="H168" s="9" t="inlineStr">
         <is>
           <t>BMC medicine</t>
         </is>
       </c>
-      <c r="I168" s="4" t="inlineStr">
+      <c r="I168" s="10" t="inlineStr">
         <is>
           <t>BACKGROUND: Computerised cognitive training (CCT) can improve the cognitive abilities of people with mild cognitive impairment (MCI), especially when the CCT contains a learning system, which is a type of machine learning (ML) that automatically selects exercises at a difficulty that corresponds to the person's peak performance and thus enables individualised training. METHODS: We developed one individualised CCT (iCCT) with ML and one basic CCT (bCCT) for an active control group (CG). The study aimed to determine whether iCCT in the intervention group (IG) resulted in significantly greater enhancements in overall cognitive functioning for individuals with MCI (age 60+) compared with bCCT in the CG across a 6-month period. This double-blind randomised controlled study was conducted entirely virtually. The 89 participants were community-dwelling people with a psychometric diagnosis of MCI living in Germany. The iCCT stimulates various cognitive functions, especially working memory, visuo-constructional reasoning, and decision-making. The bCCT includes fewer and simpler tasks. Both CCTs were used at home. At baseline and after 6 months, we assessed cognitive functioning with the Montreal Cognitive Assessment (MoCA). A mixed-model ANCOVA was conducted as the main analysis. RESULTS: Both CCTs led to significant increases in average global cognition. The estimated marginal means of the MoCA score increased significantly in the CG by an average of 0.9 points (95% CI [0.2, 1.7]) from 22.3 (SE = 0.25) to 23.2 (SE = 0.41) points (p = 0.018); in the IG, the MoCA score increased by an average of 2.2 points (95% CI [1.4, 2.9]) from 21.9 (SE = 0.26) to 24.1 (SE = 0.42) points (p &lt; 0.001). In a confound-adjusted multiple regression model, the interaction between time and group was statistically significant (F = 4.92; p = 0.029). The effect size was small to medium (partial η(2) = 0.057). On average, the participants used the CCTs three times per week with an average duration of 34.9 min per application. The iCCT was evaluated as more attractive and more stimulating than the bCCT. CONCLUSIONS: By using a multi-tasking CCT three times a week for 30 min, people with MCI living at home can significantly improve their cognitive abilities within 6 months. The use of ML significantly increases the effectiveness of cognitive training and improves user satisfaction. TRIAL REGISTRATION: ISRCTN14437015; registered February 27, 2020.</t>
         </is>
@@ -13086,31 +13136,43 @@
       </c>
     </row>
     <row r="407" ht="80" customHeight="1">
-      <c r="A407" s="2" t="n">
+      <c r="A407" s="8" t="n">
         <v>2824</v>
       </c>
-      <c r="B407" s="2" t="inlineStr"/>
-      <c r="C407" s="2" t="inlineStr"/>
-      <c r="D407" s="3" t="inlineStr"/>
-      <c r="E407" s="4" t="inlineStr">
+      <c r="B407" s="8" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C407" s="8" t="inlineStr">
+        <is>
+          <t>E1-非老年人群</t>
+        </is>
+      </c>
+      <c r="D407" s="9" t="inlineStr">
+        <is>
+          <t>阿尔茨海默病患者（第一轮漏网）</t>
+        </is>
+      </c>
+      <c r="E407" s="10" t="inlineStr">
         <is>
           <t>Effects of working memory intervention on language production by    individuals with dementia</t>
         </is>
       </c>
-      <c r="F407" s="3" t="inlineStr">
+      <c r="F407" s="9" t="inlineStr">
         <is>
           <t>Lee, Mi Sook and Kim, Bo Seon</t>
         </is>
       </c>
-      <c r="G407" s="2" t="n">
+      <c r="G407" s="8" t="n">
         <v>2021</v>
       </c>
-      <c r="H407" s="3" t="inlineStr">
+      <c r="H407" s="9" t="inlineStr">
         <is>
           <t>NEUROPSYCHOLOGICAL REHABILITATION</t>
         </is>
       </c>
-      <c r="I407" s="4" t="inlineStr">
+      <c r="I407" s="10" t="inlineStr">
         <is>
           <t>The purpose of this study was to investigate the effects of working    memory intervention on language production by people with mild or    moderate Alzheimer's disease (AD). A total of 39 AD patients, 21 with    mild AD and 18 with moderate AD and 18 normal controls were given 18    sessions of working memory intervention. After these sessions, the    transfer effects and maintenance effects at the 3-month follow-up were    assessed. A word-span task and a digit-span task were used to evaluate    working memory. Language-production abilities were compared through four    tasks: a verbal fluency, a confrontation naming, a word definition, and    a picture-description task. Task performances of working memory and    language production were the lowest in the baseline stage and the    highest in the transfer-effect stage. The three groups had transfer    effects in all tasks, while the maintenance effects were limited by    groups and tasks. This study proves that working memory intervention for    AD patients is effective for language production. In addition, we have    paved the way for working memory intervention to improve language    production by AD patients in clinical settings by presenting the    transfer and maintenance effect for each task of language production.</t>
         </is>
@@ -13582,62 +13644,86 @@
       </c>
     </row>
     <row r="423" ht="80" customHeight="1">
-      <c r="A423" s="2" t="n">
+      <c r="A423" s="8" t="n">
         <v>2913</v>
       </c>
-      <c r="B423" s="2" t="inlineStr"/>
-      <c r="C423" s="2" t="inlineStr"/>
-      <c r="D423" s="3" t="inlineStr"/>
-      <c r="E423" s="4" t="inlineStr">
+      <c r="B423" s="8" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C423" s="8" t="inlineStr">
+        <is>
+          <t>E1-非老年人群</t>
+        </is>
+      </c>
+      <c r="D423" s="9" t="inlineStr">
+        <is>
+          <t>儿童人工耳蜗（第一轮漏网）</t>
+        </is>
+      </c>
+      <c r="E423" s="10" t="inlineStr">
         <is>
           <t>Auditory Cognitive Training for Pediatric Cochlear Implant Recipients</t>
         </is>
       </c>
-      <c r="F423" s="3" t="inlineStr">
+      <c r="F423" s="9" t="inlineStr">
         <is>
           <t>Mishra, Srikanta K. and Boddupally, Shiva P.</t>
         </is>
       </c>
-      <c r="G423" s="2" t="n">
+      <c r="G423" s="8" t="n">
         <v>2018</v>
       </c>
-      <c r="H423" s="3" t="inlineStr">
+      <c r="H423" s="9" t="inlineStr">
         <is>
           <t>EAR AND HEARING</t>
         </is>
       </c>
-      <c r="I423" s="4" t="inlineStr">
+      <c r="I423" s="10" t="inlineStr">
         <is>
           <t>Objectives: Understanding speech in noise is the biggest challenge faced    by individuals with cochlear implants (CIs). Improving speech-in-noise    perception for pediatric CI recipients continues to remain a high    priority for all stakeholders. This study was designed to investigate    the efficacy of working memory training for improving speech-in-noise    recognition for children with CIs.    Design: Fourteen children with CIs (aged 6 to 15 years) received    adaptive, home-based training on forward digit span task for 5 weeks,    while 13 children with CIs participated in backward digit span training.    Seventeen age-matched children with CIs in the control group received a    placebo. Outcome measures included forward and backward digit span and    speech recognition threshold for digit triplets in noise at pretraining,    post-training, and 5-week follow-up. Performance measures from 26    age-matched children with normal hearing were also obtained only at the    baseline session to generate normative standards for comparison.    Results: Digit span scores were significantly higher at post-training    and follow-up compared with pretraining for both forward-and    backward-trained groups. Both trained groups showed similar    training-induced shifts. The control group showed no such improvement.    There was no effect of training on the speech recognition threshold.    Children with CIs showed significantly lower digit span scores and a    higher speech recognition threshold relative to children with normal    hearing.    Conclusions: Training improves working memory capacity as measured by    digit spans for children with CIs. Training-induced improvements are    stable for at least 5 weeks. Learning effects demonstrate near-transfer,    from forward to backward digit span and vice versa, but failed to show    far-transfer to speech-in-noise recognition. Current evidence is not    supportive of cognitive training for improving speech-in-noise    performance for children with CIs.</t>
         </is>
       </c>
     </row>
     <row r="424" ht="80" customHeight="1">
-      <c r="A424" s="2" t="n">
+      <c r="A424" s="8" t="n">
         <v>2931</v>
       </c>
-      <c r="B424" s="2" t="inlineStr"/>
-      <c r="C424" s="2" t="inlineStr"/>
-      <c r="D424" s="3" t="inlineStr"/>
-      <c r="E424" s="4" t="inlineStr">
+      <c r="B424" s="8" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C424" s="8" t="inlineStr">
+        <is>
+          <t>E1-非老年人群</t>
+        </is>
+      </c>
+      <c r="D424" s="9" t="inlineStr">
+        <is>
+          <t>ADHD儿童（第一轮漏网）</t>
+        </is>
+      </c>
+      <c r="E424" s="10" t="inlineStr">
         <is>
           <t>Utilizing Cognitive Training to Improve Working Memory, Attention, and    Impulsivity in School-Aged Children with ADHD and SLD</t>
         </is>
       </c>
-      <c r="F424" s="3" t="inlineStr">
+      <c r="F424" s="9" t="inlineStr">
         <is>
           <t>Wiest, Grahamm M. and Rosales, Kevin P. and Looney, Lisa and Wong,    Eugene H. and Wiest, Dudley J.</t>
         </is>
       </c>
-      <c r="G424" s="2" t="n">
+      <c r="G424" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="H424" s="3" t="inlineStr">
+      <c r="H424" s="9" t="inlineStr">
         <is>
           <t>BRAIN SCIENCES</t>
         </is>
       </c>
-      <c r="I424" s="4" t="inlineStr"/>
+      <c r="I424" s="10" t="inlineStr"/>
     </row>
     <row r="425" ht="80" customHeight="1">
       <c r="A425" s="2" t="n">
@@ -13973,31 +14059,43 @@
       <c r="I435" s="4" t="inlineStr"/>
     </row>
     <row r="436" ht="80" customHeight="1">
-      <c r="A436" s="2" t="n">
+      <c r="A436" s="8" t="n">
         <v>3424</v>
       </c>
-      <c r="B436" s="2" t="inlineStr"/>
-      <c r="C436" s="2" t="inlineStr"/>
-      <c r="D436" s="3" t="inlineStr"/>
-      <c r="E436" s="4" t="inlineStr">
+      <c r="B436" s="8" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C436" s="8" t="inlineStr">
+        <is>
+          <t>E1-非老年人群</t>
+        </is>
+      </c>
+      <c r="D436" s="9" t="inlineStr">
+        <is>
+          <t>多发性硬化患者（第一轮漏网）</t>
+        </is>
+      </c>
+      <c r="E436" s="10" t="inlineStr">
         <is>
           <t>Cognitive training improves working memory, processing speed, and neural efficiency in multiple sclerosis</t>
         </is>
       </c>
-      <c r="F436" s="3" t="inlineStr">
+      <c r="F436" s="9" t="inlineStr">
         <is>
           <t>O’Donnell, R.F.; Shucard, J.L.; Covey, T.J. et al.</t>
         </is>
       </c>
-      <c r="G436" s="2" t="n">
+      <c r="G436" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="H436" s="3" t="inlineStr">
+      <c r="H436" s="9" t="inlineStr">
         <is>
           <t>Journal of Clinical and Experimental Neuropsychology</t>
         </is>
       </c>
-      <c r="I436" s="4" t="inlineStr"/>
+      <c r="I436" s="10" t="inlineStr"/>
     </row>
     <row r="437" ht="80" customHeight="1">
       <c r="A437" s="2" t="n">
@@ -14108,31 +14206,43 @@
       <c r="I440" s="4" t="inlineStr"/>
     </row>
     <row r="441" ht="80" customHeight="1">
-      <c r="A441" s="2" t="n">
+      <c r="A441" s="8" t="n">
         <v>3801</v>
       </c>
-      <c r="B441" s="2" t="inlineStr"/>
-      <c r="C441" s="2" t="inlineStr"/>
-      <c r="D441" s="3" t="inlineStr"/>
-      <c r="E441" s="4" t="inlineStr">
+      <c r="B441" s="8" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C441" s="8" t="inlineStr">
+        <is>
+          <t>E1-非老年人群</t>
+        </is>
+      </c>
+      <c r="D441" s="9" t="inlineStr">
+        <is>
+          <t>多发性硬化患者（第一轮漏网）</t>
+        </is>
+      </c>
+      <c r="E441" s="10" t="inlineStr">
         <is>
           <t>Effects of 4-week mindfulness training versus adaptive cognitive training on processing speed and working memory in multiple sclerosis.</t>
         </is>
       </c>
-      <c r="F441" s="3" t="inlineStr">
+      <c r="F441" s="9" t="inlineStr">
         <is>
           <t>Manglani, H.R.; Samimy, S.; Schirda, B. et al.</t>
         </is>
       </c>
-      <c r="G441" s="2" t="n">
+      <c r="G441" s="8" t="n">
         <v>2020</v>
       </c>
-      <c r="H441" s="3" t="inlineStr">
+      <c r="H441" s="9" t="inlineStr">
         <is>
           <t>Neuropsychology</t>
         </is>
       </c>
-      <c r="I441" s="4" t="inlineStr"/>
+      <c r="I441" s="10" t="inlineStr"/>
     </row>
     <row r="442" ht="80" customHeight="1">
       <c r="A442" s="2" t="n">

--- a/projects/paper-01/03-screen/数据_3_第二轮人工摘要筛选.xlsx
+++ b/projects/paper-01/03-screen/数据_3_第二轮人工摘要筛选.xlsx
@@ -958,35 +958,43 @@
       </c>
     </row>
     <row r="11" ht="80" customHeight="1">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>E2-非WM训练</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>UFOV视觉训练+tDCS，非WM训练</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>The impact of a tDCS and cognitive training intervention on task-based functional connectivity.</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Kraft JN; Indahlastari A; Boutzoukas EM et al.</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>GeroScience</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Declines in several cognitive domains, most notably processing speed, occur in non-pathological aging. Given the exponential growth of the older adult population, declines in cognition serve as a significant public health issue that must be addressed. Promising studies have shown that cognitive training in older adults, particularly using the useful field of view (UFOV) paradigm, can improve cognition with moderate to large effect sizes. Additionally, meta-analyses have found that transcranial direct current stimulation (tDCS), a non-invasive form of brain stimulation, can improve cognition in attention/processing speed and working memory. However, only a handful of studies have looked at concomitant tDCS and cognitive training, usually with short interventions and small sample sizes. The current study assessed the effect of a tDCS (active versus sham) and a 3-month cognitive training intervention on task-based functional connectivity during completion of the UFOV task in a large older adult sample (N = 153). We found significant increased functional connectivity between the left and right pars triangularis (the ROIs closest to the electrodes) following active, but not sham tDCS. Additionally, we see trending behavioral improvements associated with these functional connectivity changes in the active tDCS group, but not sham. Collectively, these findings suggest that tDCS and cognitive training can be an effective modulator of task-based functional connectivity above and beyond a cognitive training intervention alone.</t>
         </is>
@@ -1141,35 +1149,43 @@
       </c>
     </row>
     <row r="16" ht="80" customHeight="1">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>E3-无认知结局</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>仅报告功能网络重构，无行为认知结局</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Age differences in functional network reconfiguration with working memory training.</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Iordan AD; Moored KD; Katz B et al.</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G16" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Human brain mapping</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>Demanding cognitive functions like working memory (WM) depend on functional brain networks being able to communicate efficiently while also maintaining some degree of modularity. Evidence suggests that aging can disrupt this balance between integration and modularity. In this study, we examined how cognitive training affects the integration and modularity of functional networks in older and younger adults. Twenty three younger and 23 older adults participated in 10 days of verbal WM training, leading to performance gains in both age groups. Older adults exhibited lower modularity overall and a greater decrement when switching from rest to task, compared to younger adults. Interestingly, younger but not older adults showed increased task-related modularity with training. Furthermore, whereas training increased efficiency within, and decreased participation of, the default-mode network for younger adults, it enhanced efficiency within a task-specific salience/sensorimotor network for older adults. Finally, training increased segregation of the default-mode from frontoparietal/salience and visual networks in younger adults, while it diffusely increased between-network connectivity in older adults. Thus, while younger adults increase network segregation with training, suggesting more automated processing, older adults persist in, and potentially amplify, a more integrated and costly global workspace, suggesting different age-related trajectories in functional network reorganization with WM training.</t>
         </is>
@@ -1566,35 +1582,43 @@
       </c>
     </row>
     <row r="27" ht="80" customHeight="1">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="2" t="n">
         <v>139</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>E1-非老年人群</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>术后住院老年人，非健康老年人</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Working Memory Training for Older Adults After Major Surgery: Benefits to Cognitive and Emotional Functioning.</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Carbone E; Vianello E; Carretti B et al.</t>
         </is>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="G27" s="2" t="n">
         <v>2019</v>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>The American journal of geriatric psychiatry : official journal of the American Association for Geriatric Psychiatry</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>OBJECTIVES: Cognitive and mood changes can affect postoperative recovery in hospitalized older adults undergoing major surgical procedures, but few studies have considered postoperative cognitive interventions to sustain such patients' cognitive functioning and mood. The aim of this pilot study was to assess the efficacy of working memory training in improving cognitive functioning and mood, or emotional functioning, in older adults undergoing major surgery. METHODS: Thirty-four older adults (from 64 to 75 years of age) hospitalized for partial or total arthroplasty of the knee were randomly assigned to either a trained group (N = 18) or an active control group (N = 16). The former received working memory training during the postoperative period, while the latter engaged in alternative activities. In addition to specific training gains in a working memory task similar to the one used in the training (criterion task), transfer effects to cognitive abilities (short- and long-term memory, and cognitive inhibition), and mood or emotional functioning (signs of depression or anxiety) were investigated. RESULTS: Immediately after the training, results showed a main effect of group (in favor of the trained group) in the criterion task, in one of the short-term memory measures, and in cognitive inhibition. In addition, only the trained group showed a decrease in depression and anxiety scores. CONCLUSION: The results of this pilot study suggest that cognitive training targeting working memory administered in the postoperative period after major surgery can sustain older adults' cognitive and emotional functioning, and especially their mood.</t>
         </is>
@@ -1878,35 +1902,43 @@
       </c>
     </row>
     <row r="35" ht="80" customHeight="1">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="2" t="n">
         <v>184</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>E3-无认知结局</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>仅报告MRI数据，无行为认知结局</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>The gains of a 4-week cognitive training are not modulated by novelty.</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Biel D; Steiger TK; Volkmann T et al.</t>
         </is>
       </c>
-      <c r="G35" s="5" t="n">
+      <c r="G35" s="2" t="n">
         <v>2020</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>Human brain mapping</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>Cognitive training should not only improve performance of the trained task, but also untrained abilities. Exposure to novelty can improve subsequent memory performance, suggesting that novelty exposure might be a critical factor to promote the effects of cognitive training. Therefore, we combined a 4-week working memory training with novelty exposure. Neuropsychological tests and MRI data were acquired before and after training to analyze behavior and changes in gray matter volume, myelination, and iron levels. In total, 83 healthy older humans participated in one of three groups: Two groups completed a 4-week computerized cognitive training of a two-back working memory task, either in combination with novel or with familiarized nature movies. A third group did not receive any training. As expected, both training groups showed improvements in task specific working memory performance and reaction times. However, there were no transfer or novelty effects on fluid intelligence, verbal memory, digit-span, and executive functions. At the neural level, no significant micro- or macrostructural changes emerged in either group. Our findings suggest that working memory training in healthy older adults is associated with task-specific improvements, but these gains do not transfer to other cognitive domains, and it does not lead to structural brain changes.</t>
         </is>
@@ -2408,35 +2440,43 @@
       </c>
     </row>
     <row r="49" ht="80" customHeight="1">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="2" t="n">
         <v>249</v>
       </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="6" t="n"/>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>E3-无认知结局</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>仅报告神经相关物，无行为认知结局</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>Neural correlates of training and transfer effects in working memory in older adults.</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Heinzel S; Lorenz RC; Pelz P et al.</t>
         </is>
       </c>
-      <c r="G49" s="5" t="n">
+      <c r="G49" s="2" t="n">
         <v>2016</v>
       </c>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>NeuroImage</t>
         </is>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="I49" s="4" t="inlineStr">
         <is>
           <t>As indicated by previous research, aging is associated with a decline in working memory (WM) functioning, related to alterations in fronto-parietal neural activations. At the same time, previous studies showed that WM training in older adults may improve the performance in the trained task (training effect), and more importantly, also in untrained WM tasks (transfer effects). However, neural correlates of these transfer effects that would improve understanding of its underlying mechanisms, have not been shown in older participants as yet. In this study, we investigated blood-oxygen-level-dependent (BOLD) signal changes during n-back performance and an untrained delayed recognition (Sternberg) task following 12sessions (45min each) of adaptive n-back training in older adults. The Sternberg task used in this study allowed to test for neural training effects independent of specific task affordances of the trained task and to separate maintenance from updating processes. Thirty-two healthy older participants (60-75years) were assigned either to an n-back training or a no-contact control group. Before (t1) and after (t2) training/waiting period, both the n-back task and the Sternberg task were conducted while BOLD signal was measured using functional Magnetic Resonance Imaging (fMRI) in all participants. In addition, neuropsychological tests were performed outside the scanner. WM performance improved with training and behavioral transfer to tests measuring executive functions, processing speed, and fluid intelligence was found. In the training group, BOLD signal in the right lateral middle frontal gyrus/caudal superior frontal sulcus (Brodmann area, BA 6/8) decreased in both the trained n-back and the updating condition of the untrained Sternberg task at t2, compared to the control group. fMRI findings indicate a training-related increase in processing efficiency of WM networks, potentially related to the process of WM updating. Performance gains in untrained tasks suggest that transfer to other cognitive tasks remains possible in aging.</t>
         </is>
@@ -2556,35 +2596,43 @@
       </c>
     </row>
     <row r="53" ht="80" customHeight="1">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="2" t="n">
         <v>264</v>
       </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>E2-非WM训练</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>知觉训练(perceptual training)，非WM训练</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>The influence of perceptual training on working memory in older adults.</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Berry AS; Zanto TP; Clapp WC et al.</t>
         </is>
       </c>
-      <c r="G53" s="5" t="n">
+      <c r="G53" s="2" t="n">
         <v>2010</v>
       </c>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>PloS one</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="I53" s="4" t="inlineStr">
         <is>
           <t>Normal aging is associated with a degradation of perceptual abilities and a decline in higher-level cognitive functions, notably working memory. To remediate age-related deficits, cognitive training programs are increasingly being developed. However, it is not yet definitively established if, and by what mechanisms, training ameliorates effects of cognitive aging. Furthermore, a major factor impeding the success of training programs is a frequent failure of training to transfer benefits to untrained abilities. Here, we offer the first evidence of direct transfer-of-benefits from perceptual discrimination training to working memory performance in older adults. Moreover, using electroencephalography to evaluate participants before and after training, we reveal neural evidence of functional plasticity in older adult brains, such that training-induced modifications in early visual processing during stimulus encoding predict working memory accuracy improvements. These findings demonstrate the strength of the perceptual discrimination training approach by offering clear psychophysical evidence of transfer-of-benefit and a neural mechanism underlying cognitive improvement.</t>
         </is>
@@ -3333,35 +3381,43 @@
       </c>
     </row>
     <row r="72" ht="80" customHeight="1">
-      <c r="A72" s="5" t="n">
+      <c r="A72" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="n"/>
-      <c r="D72" s="6" t="n"/>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>E2-非WM训练</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>多类型认知训练对比，WM非主要成分</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t>Effects of Different Types of Cognitive Training on Cognitive Function, Brain Structure, and Driving Safety in Senior Daily Drivers: A Pilot Study.</t>
         </is>
       </c>
-      <c r="F72" s="6" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>Nozawa T; Taki Y; Kanno A et al.</t>
         </is>
       </c>
-      <c r="G72" s="5" t="n">
+      <c r="G72" s="2" t="n">
         <v>2015</v>
       </c>
-      <c r="H72" s="6" t="inlineStr">
+      <c r="H72" s="3" t="inlineStr">
         <is>
           <t>Behavioural neurology</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
+      <c r="I72" s="4" t="inlineStr">
         <is>
           <t>BACKGROUND: Increasing proportion of the elderly in the driving population raises the importance of assuring their safety. We explored the effects of three different types of cognitive training on the cognitive function, brain structure, and driving safety of the elderly. METHODS: Thirty-seven healthy elderly daily drivers were randomly assigned to one of three training groups: Group V trained in a vehicle with a newly developed onboard cognitive training program, Group P trained with a similar program but on a personal computer, and Group C trained to solve a crossword puzzle. Before and after the 8-week training period, they underwent neuropsychological tests, structural brain magnetic resonance imaging, and driving safety tests. RESULTS: For cognitive function, only Group V showed significant improvements in processing speed and working memory. For driving safety, Group V showed significant improvements both in the driving aptitude test and in the on-road evaluations. Group P showed no significant improvements in either test, and Group C showed significant improvements in the driving aptitude but not in the on-road evaluations. CONCLUSION: The results support the effectiveness of the onboard training program in enhancing the elderly's abilities to drive safely and the potential advantages of a multimodal training approach.</t>
         </is>
@@ -3946,70 +4002,86 @@
       </c>
     </row>
     <row r="87" ht="80" customHeight="1">
-      <c r="A87" s="5" t="n">
+      <c r="A87" s="2" t="n">
         <v>510</v>
       </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="n"/>
-      <c r="D87" s="6" t="n"/>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>E2-非WM训练</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>VIRTRAEL多域训练+Facebook，非WM训练</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t>Does Including Facebook Training Improve the Effectiveness of Computerized Cognitive Training? A Randomized Controlled Trial.</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>Rute-Pérez S; Rodríguez-Domínguez C; Sánchez-Lara EM et al.</t>
         </is>
       </c>
-      <c r="G87" s="5" t="n">
+      <c r="G87" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="H87" s="6" t="inlineStr">
+      <c r="H87" s="3" t="inlineStr">
         <is>
           <t>Clinical rehabilitation</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr">
+      <c r="I87" s="4" t="inlineStr">
         <is>
           <t>OBJECTIVE: To determine whether implementing a Facebook training program improves the effectiveness of computerized cognitive training (CCT) in older adults. DESIGN: Randomized, controlled, double single-blind trial with parallel groups. SETTING: Community centers. SUBJECTS: Eighty-six adults between 60 and 90 years old. INTERVENTIONS: Nine face-to-face 60-min sessions of CCT with VIRTRAEL for all participants. The experimental group received an additional 30 min of Facebook training per session. MAIN MEASURES: Attention (d2 Test of Attention); learning and verbal memory (Hopkins Verbal Learning Test-Revised); working memory (Letter-Number Sequencing test), semantic and abstract reasoning (Similarities and Matrix Reasoning tests); and planning (Key Search test). RESULTS: There was a significant Group*Time interaction in the Hopkins Verbal Learning Test-Revised-Trial 3, Letter-Number sequencing, and Matrix tests. Between groups, post-hoc analyses showed a difference in Matrix reasoning (p &lt; .001; d  =  0.893) at post-intervention in favor of the experimental group. Significant main effects of time were found in the CCT group between baseline and 3-month follow-up for Concentration (F  =  26.431, p ≤ .001), Letters and Numbers (F  =  30.549, p ≤ .001), Learning (F  =  38.678, p ≤ .001), Similarities (F  =  69.885, p ≤ .001), Matrix (F  =  90.342, p ≤ .001), and Key Search (F  =  7.904, p  =  .006) tests. CONCLUSIONS: The utilization of CCT with VIRTRAEL, a freely accessible tool with broad applicability, resulted in enhanced attention, verbal learning, working memory, abstract and semantic reasoning, and planning among older adults. These improvements were sustained for at least three months post-training. Additional training in Facebook did not enhance the effectiveness of CCT.</t>
         </is>
       </c>
     </row>
     <row r="88" ht="80" customHeight="1">
-      <c r="A88" s="5" t="n">
+      <c r="A88" s="2" t="n">
         <v>512</v>
       </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="n"/>
-      <c r="D88" s="6" t="n"/>
-      <c r="E88" s="7" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>E3-无认知结局</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>仅报告脑激活泛化，无行为认知结局</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
         <is>
           <t>Brain activations elicited during task-switching generalize beyond the task: A partial least squares correlation approach to combine fMRI signals and cognition.</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
+      <c r="F88" s="3" t="inlineStr">
         <is>
           <t>Skolasinska P; Qin S; Voss M et al.</t>
         </is>
       </c>
-      <c r="G88" s="5" t="n">
+      <c r="G88" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="H88" s="6" t="inlineStr">
+      <c r="H88" s="3" t="inlineStr">
         <is>
           <t>Human brain mapping</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
+      <c r="I88" s="4" t="inlineStr">
         <is>
           <t>An underlying hypothesis for broad transfer from cognitive training is that the regional brain signals engaged during the training task are related to the transfer tasks. However, it is unclear whether the brain activations elicited from a specific cognitive task can generalize to performance of other tasks, esp. in normal aging where cognitive training holds much promise. In this large dual-site functional magnetic resonance imaging (fMRI) study, we aimed to characterize the neurobehavioral correlates of task-switching in normal aging and examine whether the task-switching-related fMRI-blood-oxygen-level-dependent (BOLD) signals, engaged during varieties of cognitive control, generalize to other tasks of executive control and general cognition. We therefore used a hybrid blocked and event-related fMRI task-switching paradigm to investigate brain regions associated with multiple types of cognitive control on 129 non-demented older adults (65-85 years). This large dataset provided a unique opportunity for a data-driven partial least squares-correlation approach to investigate the generalizability of multiple fMRI-BOLD signals associated with task-switching costs to other tasks of executive control, general cognition, and demographic characteristics. While some fMRI signals generalized beyond the scanned task, others did not. Results indicate right middle frontal brain activation as detrimental to task-switching performance, whereas inferior frontal and caudate activations were related to faster processing speed during the fMRI task-switching, but activations of these regions did not predict performance on other tasks of executive control or general cognition. However, BOLD signals from the right lateral occipital cortex engaged during the fMRI task positively predicted performance on a working memory updating task, and BOLD signals from the left post-central gyrus that were disengaged during the fMRI task were related to slower processing speed in the task as well as to lower general cognition. Together, these results suggest generalizability of these BOLD signals beyond the scanned task. The findings also provided evidence for the general slowing hypothesis of aging as most variance in the data were explained by low processing speed and global low BOLD signal in older age. As processing speed shared variance with task-switching and other executive control tasks, it might be a possible basis of generalizability between these tasks. Additional results support the dedifferentiation hypothesis of brain aging, as right middle frontal activations predicted poorer task-switching performance. Overall, we observed that the BOLD signals related to the fMRI task not only generalize to the performance of other executive control tasks, but unique brain predictors of out-of-scanner performance can be identified.</t>
         </is>
@@ -4258,35 +4330,43 @@
       </c>
     </row>
     <row r="95" ht="80" customHeight="1">
-      <c r="A95" s="5" t="n">
+      <c r="A95" s="2" t="n">
         <v>587</v>
       </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="n"/>
-      <c r="D95" s="6" t="n"/>
-      <c r="E95" s="7" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>E1-非老年人群</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>中年成人为主，无≥60岁老年组</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
         <is>
           <t>Dual N-Back Working Memory Training in Healthy Adults: A Randomized Comparison to Processing Speed Training.</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr">
+      <c r="F95" s="3" t="inlineStr">
         <is>
           <t>Lawlor-Savage L; Goghari VM</t>
         </is>
       </c>
-      <c r="G95" s="5" t="n">
+      <c r="G95" s="2" t="n">
         <v>2016</v>
       </c>
-      <c r="H95" s="6" t="inlineStr">
+      <c r="H95" s="3" t="inlineStr">
         <is>
           <t>PloS one</t>
         </is>
       </c>
-      <c r="I95" s="7" t="inlineStr">
+      <c r="I95" s="4" t="inlineStr">
         <is>
           <t>Enhancing cognitive ability is an attractive concept, particularly for middle-aged adults interested in maintaining cognitive functioning and preventing age-related declines. Computerized working memory training has been investigated as a safe method of cognitive enhancement in younger and older adults, although few studies have considered the potential impact of working memory training on middle-aged adults. This study investigated dual n-back working memory training in healthy adults aged 30-60. Fifty-seven adults completed measures of working memory, processing speed, and fluid intelligence before and after a 5-week web-based dual n-back or active control (processing speed) training program. RESULTS: Repeated measures multivariate analysis of variance failed to identify improvements across the three cognitive composites, working memory, processing speed, and fluid intelligence, after training. Follow-up Bayesian analyses supported null findings for training effects for each individual composite. Findings suggest that dual n-back working memory training may not benefit working memory or fluid intelligence in healthy adults. Further investigation is necessary to clarify if other forms of working memory training may be beneficial, and what factors impact training-related benefits, should they occur, in this population.</t>
         </is>
@@ -4594,35 +4674,43 @@
       </c>
     </row>
     <row r="103" ht="80" customHeight="1">
-      <c r="A103" s="5" t="n">
+      <c r="A103" s="2" t="n">
         <v>662</v>
       </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C103" s="5" t="n"/>
-      <c r="D103" s="6" t="n"/>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>E3-无认知结局</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>仅报告脑动态模式，无行为认知结局</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
         <is>
           <t>Working Memory and Reasoning Benefit from Different Modes of Large-scale Brain Dynamics in Healthy Older Adults.</t>
         </is>
       </c>
-      <c r="F103" s="6" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t>Lebedev AV; Nilsson J; Lövdén M</t>
         </is>
       </c>
-      <c r="G103" s="5" t="n">
+      <c r="G103" s="2" t="n">
         <v>2018</v>
       </c>
-      <c r="H103" s="6" t="inlineStr">
+      <c r="H103" s="3" t="inlineStr">
         <is>
           <t>Journal of cognitive neuroscience</t>
         </is>
       </c>
-      <c r="I103" s="7" t="inlineStr">
+      <c r="I103" s="4" t="inlineStr">
         <is>
           <t>Researchers have proposed that solving complex reasoning problems, a key indicator of fluid intelligence, involves the same cognitive processes as solving working memory tasks. This proposal is supported by an overlap of the functional brain activations associated with the two types of tasks and by high correlations between interindividual differences in performance. We replicated these findings in 53 older participants but also showed that solving reasoning and working memory problems benefits from different configurations of the functional connectome and that this dissimilarity increases with a higher difficulty load. Specifically, superior performance in a typical working memory paradigm ( n-back) was associated with upregulation of modularity (increased between-network segregation), whereas performance in the reasoning task was associated with effective downregulation of modularity. We also showed that working memory training promotes task-invariant increases in modularity. Because superior reasoning performance is associated with downregulation of modular dynamics, training may thus have fostered an inefficient way of solving the reasoning tasks. This could help explain why working memory training does little to promote complex reasoning performance. The study concludes that complex reasoning abilities cannot be reduced to working memory and suggests the need to reconsider the feasibility of using working memory training interventions to attempt to achieve effects that transfer to broader cognition.</t>
         </is>
@@ -4957,35 +5045,43 @@
       </c>
     </row>
     <row r="112" ht="80" customHeight="1">
-      <c r="A112" s="5" t="n">
+      <c r="A112" s="2" t="n">
         <v>721</v>
       </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="n"/>
-      <c r="D112" s="6" t="n"/>
-      <c r="E112" s="7" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>E3-无认知结局</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>仅报告白质完整性，无行为认知结局</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
         <is>
           <t>Working Memory Training Effects on White Matter Integrity in Young and Older Adults.</t>
         </is>
       </c>
-      <c r="F112" s="6" t="inlineStr">
+      <c r="F112" s="3" t="inlineStr">
         <is>
           <t>Dziemian S; Appenzeller S; von Bastian CC et al.</t>
         </is>
       </c>
-      <c r="G112" s="5" t="n">
+      <c r="G112" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="H112" s="6" t="inlineStr">
+      <c r="H112" s="3" t="inlineStr">
         <is>
           <t>Frontiers in human neuroscience</t>
         </is>
       </c>
-      <c r="I112" s="7" t="inlineStr">
+      <c r="I112" s="4" t="inlineStr">
         <is>
           <t>OBJECTIVES: Working memory is essential for daily life skills like reading comprehension, reasoning, and problem-solving. Healthy aging of the brain goes along with working memory decline that can affect older people's independence in everyday life. Interventions in the form of cognitive training are a promising tool for delaying age-related working memory decline, yet the underlying structural plasticity of white matter is hardly studied. METHODS: We conducted a longitudinal diffusion tensor imaging study to investigate the effects of an intensive four-week adaptive working memory training on white matter integrity quantified by global and tract-wise mean diffusivity. We compared diffusivity measures of fiber tracts that are associated with working memory of 32 young and 20 older participants that were randomly assigned to a working memory training group or an active control group. RESULTS: The behavioral analysis showed an increase in working memory performance after the four-week adaptive working memory training. The neuroanatomical analysis revealed a decrease in mean diffusivity in the working memory training group after the training intervention in the right inferior longitudinal fasciculus for the older adults. There was also a decrease in mean diffusivity in the working memory training group in the right superior longitudinal fasciculus for the older and young participants after the intervention. CONCLUSION: This study shows that older people can benefit from working memory training by improving their working memory performance that is also reflected in terms of improved white matter integrity in the superior longitudinal fasciculus and the inferior longitudinal fasciculus, where the first is an essential component of the frontoparietal network known to be essential in working memory.</t>
         </is>
@@ -5035,35 +5131,43 @@
       </c>
     </row>
     <row r="114" ht="80" customHeight="1">
-      <c r="A114" s="5" t="n">
+      <c r="A114" s="2" t="n">
         <v>730</v>
       </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="n"/>
-      <c r="D114" s="6" t="n"/>
-      <c r="E114" s="7" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>E3-无认知结局</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>仅报告DLPFC功能连接，无行为认知结局</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
         <is>
           <t>Dorsolateral Prefrontal Functional Connectivity Predicts Working Memory Training Gains.</t>
         </is>
       </c>
-      <c r="F114" s="6" t="inlineStr">
+      <c r="F114" s="3" t="inlineStr">
         <is>
           <t>Faraza S; Waldenmaier J; Dyrba M et al.</t>
         </is>
       </c>
-      <c r="G114" s="5" t="n">
+      <c r="G114" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="H114" s="6" t="inlineStr">
+      <c r="H114" s="3" t="inlineStr">
         <is>
           <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
-      <c r="I114" s="7" t="inlineStr">
+      <c r="I114" s="4" t="inlineStr">
         <is>
           <t>Background: Normal aging is associated with working memory decline. A decrease in working memory performance is associated with age-related changes in functional activation patterns in the dorsolateral prefrontal cortex (DLPFC). Cognitive training can improve cognitive performance in healthy older adults. We implemented a cognitive training study to assess determinants of generalization of training gains to untrained tasks, a key indicator for the effectiveness of cognitive training. We aimed to investigate the association of resting-state functional connectivity (FC) of DLPFC with working memory performance improvement and cognitive gains after the training. Method: A sample of 60 healthy older adults (mean age: 68 years) underwent a 4-week neuropsychological training, entailing a working memory task. Baseline resting-state functional MRI (rs-fMRI) images were acquired in order to investigate the FC of DLPFC. To evaluate training effects, participants underwent a neuropsychological assessment before and after the training. A second follow-up assessment was applied 12 weeks after the training. We used cognitive scores of digit span backward and visual block span backward tasks representing working memory function. The training group was divided into subjects who had and who did not have training gains, which was defined as a higher improvement in working memory tasks than the control group (N = 19). Results: A high FC of DLPFC of the right hemisphere was significantly associated with training gains and performance improvement in the visuospatial task. The maintenance of cognitive gains was restricted to the time period directly after the training. The training group showed performance improvement in the digit span backward task. Conclusion: Functional activation patterns of the DLPFC were associated with the degree of working memory training gains and visuospatial performance improvement. Although improvement through cognitive training and acquisition of training gains are possible in aging, they remain limited.</t>
         </is>
@@ -5554,35 +5658,43 @@
       </c>
     </row>
     <row r="127" ht="80" customHeight="1">
-      <c r="A127" s="5" t="n">
+      <c r="A127" s="2" t="n">
         <v>827</v>
       </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C127" s="5" t="n"/>
-      <c r="D127" s="6" t="n"/>
-      <c r="E127" s="7" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>E1-非老年人群</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>中年健康成人，非老年人群</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
         <is>
           <t>Computerised working memory training in healthy adults: a comparison of two different training schedules.</t>
         </is>
       </c>
-      <c r="F127" s="6" t="inlineStr">
+      <c r="F127" s="3" t="inlineStr">
         <is>
           <t>Penner IK; Vogt A; Stöcklin M et al.</t>
         </is>
       </c>
-      <c r="G127" s="5" t="n">
+      <c r="G127" s="2" t="n">
         <v>2012</v>
       </c>
-      <c r="H127" s="6" t="inlineStr">
+      <c r="H127" s="3" t="inlineStr">
         <is>
           <t>Neuropsychological rehabilitation</t>
         </is>
       </c>
-      <c r="I127" s="7" t="inlineStr">
+      <c r="I127" s="4" t="inlineStr">
         <is>
           <t>This study compared a high intensity working memory training (45 minutes, 4 times per week for 4 weeks) with a distributed training (45 minutes, 2 times per week for 8 weeks) in middle-aged, healthy adults. The aim was to clarify whether a computerised working memory training is effective and whether intensity of training influences training outcome. To evaluate the efficacy and possible transfer effects, a neuropsychological test battery assessing short- and long-term memory, working memory, executive functions and mental speed was applied at baseline and at retest. Our results indicate that the distributed training led to increased performance in all cognitive domains when compared to the high intensity training and the control group without training. The most significant differences revealed by interaction contrasts were found for verbal and visual working memory, verbal short-term memory and mental speed. These results support the hypothesis that cognitive enhancement by cognitive intervention is effective in healthy individuals, and that a distributed training schedule is superior to a high intensity intervention.</t>
         </is>
@@ -5788,35 +5900,43 @@
       </c>
     </row>
     <row r="133" ht="80" customHeight="1">
-      <c r="A133" s="5" t="n">
+      <c r="A133" s="2" t="n">
         <v>867</v>
       </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C133" s="5" t="n"/>
-      <c r="D133" s="6" t="n"/>
-      <c r="E133" s="7" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>E1-非老年人群</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>含神经退行性疾病患者，非健康老年人</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
         <is>
           <t>Machine learning and individual variability in electric field characteristics predict tDCS treatment response.</t>
         </is>
       </c>
-      <c r="F133" s="6" t="inlineStr">
+      <c r="F133" s="3" t="inlineStr">
         <is>
           <t>Albizu A; Fang R; Indahlastari A et al.</t>
         </is>
       </c>
-      <c r="G133" s="5" t="n">
+      <c r="G133" s="2" t="n">
         <v>2020</v>
       </c>
-      <c r="H133" s="6" t="inlineStr">
+      <c r="H133" s="3" t="inlineStr">
         <is>
           <t>Brain stimulation</t>
         </is>
       </c>
-      <c r="I133" s="7" t="inlineStr">
+      <c r="I133" s="4" t="inlineStr">
         <is>
           <t>BACKGROUND: Transcranial direct current stimulation (tDCS) is widely investigated as a therapeutic tool to enhance cognitive function in older adults with and without neurodegenerative disease. Prior research demonstrates that electric current delivery to the brain can vary significantly across individuals. Quantification of this variability could enable person-specific optimization of tDCS outcomes. This pilot study used machine learning and MRI-derived electric field models to predict working memory improvements as a proof of concept for precision cognitive intervention. METHODS: Fourteen healthy older adults received 20 minutes of 2 mA tDCS stimulation (F3/F4) during a two-week cognitive training intervention. Participants performed an N-back working memory task pre-/post-intervention. MRI-derived current models were passed through a linear Support Vector Machine (SVM) learning algorithm to characterize crucial tDCS current components (intensity and direction) that induced working memory improvements in tDCS responders versus non-responders. MAIN RESULTS: SVM models of tDCS current components had 86% overall accuracy in classifying treatment responders vs. non-responders, with current intensity producing the best overall model differentiating changes in working memory performance. Median current intensity and direction in brain regions near the electrodes were positively related to intervention responses (r=0.811,p&lt;0.001 and r=0.774,p=0.001). CONCLUSIONS: This study provides the first evidence that pattern recognition analyses of MRI-derived tDCS current models can provide individual prognostic classification of tDCS treatment response with 86% accuracy. Individual differences in current intensity and direction play important roles in determining treatment response to tDCS. These findings provide important insights into mechanisms of tDCS response as well as proof of concept for future precision dosing models of tDCS intervention.</t>
         </is>
@@ -9707,35 +9827,43 @@
       </c>
     </row>
     <row r="226" ht="80" customHeight="1">
-      <c r="A226" s="5" t="n">
+      <c r="A226" s="2" t="n">
         <v>1748</v>
       </c>
-      <c r="B226" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C226" s="5" t="n"/>
-      <c r="D226" s="6" t="n"/>
-      <c r="E226" s="7" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>E3-无认知结局</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>仅报告网络属性，无行为认知结局</t>
+        </is>
+      </c>
+      <c r="E226" s="4" t="inlineStr">
         <is>
           <t>Aging and Network Properties: Stability Over Time and Links with Learning during Working Memory Training.</t>
         </is>
       </c>
-      <c r="F226" s="6" t="inlineStr">
+      <c r="F226" s="3" t="inlineStr">
         <is>
           <t>Iordan AD; Cooke KA; Moored KD et al.</t>
         </is>
       </c>
-      <c r="G226" s="5" t="n">
+      <c r="G226" s="2" t="n">
         <v>2017</v>
       </c>
-      <c r="H226" s="6" t="inlineStr">
+      <c r="H226" s="3" t="inlineStr">
         <is>
           <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
-      <c r="I226" s="7" t="inlineStr">
+      <c r="I226" s="4" t="inlineStr">
         <is>
           <t>Growing evidence suggests that healthy aging affects the configuration of large-scale functional brain networks. This includes reducing network modularity and local efficiency. However, the stability of these effects over time and their potential role in learning remain poorly understood. The goal of the present study was to further clarify previously reported age effects on "resting-state" networks, to test their reliability over time, and to assess their relation to subsequent learning during training. Resting-state fMRI data from 23 young (YA) and 20 older adults (OA) were acquired in 2 sessions 2 weeks apart. Graph-theoretic analyses identified both consistencies in network structure and differences in module composition between YA and OA, suggesting topological changes and less stability of functional network configuration with aging. Brain-wide, OA showed lower modularity and local efficiency compared to YA, consistent with the idea of age-related functional dedifferentiation, and these effects were replicable over time. At the level of individual networks, OA consistently showed greater participation and lower local efficiency and within-network connectivity in the cingulo-opercular network, as well as lower intra-network connectivity in the default-mode network and greater participation of the somato-sensorimotor network, suggesting age-related differential effects at the level of specialized brain modules. Finally, brain-wide network properties showed associations, albeit limited, with learning rates, as assessed with 10 days of computerized working memory training administered after the resting-state sessions, suggesting that baseline network configuration may influence subsequent learning outcomes. Identification of neural mechanisms associated with learning-induced plasticity is important for further clarifying whether and how such changes predict the magnitude and maintenance of training gains, as well as the extent and limits of cognitive transfer in both younger and older adults.</t>
         </is>
@@ -9785,35 +9913,43 @@
       </c>
     </row>
     <row r="228" ht="80" customHeight="1">
-      <c r="A228" s="5" t="n">
+      <c r="A228" s="2" t="n">
         <v>1753</v>
       </c>
-      <c r="B228" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C228" s="5" t="n"/>
-      <c r="D228" s="6" t="n"/>
-      <c r="E228" s="7" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>E3-无认知结局</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>仅报告theta/alpha脑电，无行为认知结局</t>
+        </is>
+      </c>
+      <c r="E228" s="4" t="inlineStr">
         <is>
           <t>Cognitive training and retest learning effects on theta and alpha power in older and young adults: A perspective on the crunch hypothesis and the STAC-R model.</t>
         </is>
       </c>
-      <c r="F228" s="6" t="inlineStr">
+      <c r="F228" s="3" t="inlineStr">
         <is>
           <t>Zając-Lamparska L; Zabielska-Mendyk E; Zapała D et al.</t>
         </is>
       </c>
-      <c r="G228" s="5" t="n">
+      <c r="G228" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="H228" s="6" t="inlineStr">
+      <c r="H228" s="3" t="inlineStr">
         <is>
           <t>International journal of clinical and health psychology : IJCHP</t>
         </is>
       </c>
-      <c r="I228" s="7" t="inlineStr">
+      <c r="I228" s="4" t="inlineStr">
         <is>
           <t>According to the STAC-R model, scaffolding enhancement is achievable through various interventions. Indicating forms of compensatory scaffolding, the STAC-R model refers to phenomena described in other theoretical models, such as the enhanced fronto-parietal recruitment described in the CRUNCH hypothesis. The presented study investigated whether working memory training can induce compensatory scaffolding in older adults through increased prefrontal and parietal involvement (indicated by changes in theta and alpha power). The sample comprised 90 individuals, including 45 participants from the experimental (22 older and 23 young adults) and 45 from the passive control group (21 older and 24 young adults). The age range was 60-75 years for older adults and 20-35 years for young adults. We assessed the effects of a 12-session working memory training with the use of the adaptive n-back task on theta and alpha power measured in frontal midline and central-parietal areas by EEG in older and young adults during the n-back task performance at three difficulty levels. At the behavioral level, we found a positive, significant improvement in cognitive performance in young adults from experimental group. In contrast, the positive changes in older adults were too small to prove statistically significant. At the level of neuronal activity, we observed not a training effect but a retest effect. It was revealed primarily for theta oscillations in older adults and manifested by increased theta power with higher task demands and equalization of theta power of older and younger persons in the post-test. For alpha oscillations, the retest effect was negligible, and its only manifestation observed in older adults was a reduction in the dependence of alpha power on task difficulty. The study results indicate limited potential for improving WM performance in older adults compared to young adults. The presence of the retest learning effect, instead of the training effect, proved that familiarity with the task was crucial, rather than regular training of its performance. Changes observed in older adults in theta power can be considered positive, and these results are consistent with the CRUNCH hypothesis of a compensatory role for increased executive control involvement. In turn, changes in the alpha power in the same group should be considered rather maladaptive. Nevertheless, given the overall study findings, it can be concluded that although the behavioral effects of training are stronger in young adults, the changes in neuronal activity resulting from the retest learning effect are more marked in older adults.</t>
         </is>
@@ -9863,70 +9999,86 @@
       </c>
     </row>
     <row r="230" ht="80" customHeight="1">
-      <c r="A230" s="5" t="n">
+      <c r="A230" s="2" t="n">
         <v>1760</v>
       </c>
-      <c r="B230" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C230" s="5" t="n"/>
-      <c r="D230" s="6" t="n"/>
-      <c r="E230" s="7" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>E2-非WM训练</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>二分听觉训练+执行意图策略训练，非WM训练</t>
+        </is>
+      </c>
+      <c r="E230" s="4" t="inlineStr">
         <is>
           <t>Fostering cognitive performance in older adults with a process- and a strategy-based cognitive training.</t>
         </is>
       </c>
-      <c r="F230" s="6" t="inlineStr">
+      <c r="F230" s="3" t="inlineStr">
         <is>
           <t>Studer-Luethi B; Boesch V; Lusti S et al.</t>
         </is>
       </c>
-      <c r="G230" s="5" t="n">
+      <c r="G230" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="H230" s="6" t="inlineStr">
+      <c r="H230" s="3" t="inlineStr">
         <is>
           <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
         </is>
       </c>
-      <c r="I230" s="7" t="inlineStr">
+      <c r="I230" s="4" t="inlineStr">
         <is>
           <t>The present study investigates the impact of process-based and strategy-based cognitive training to boost performance in healthy older adults. Three groups trained with either a dichotic listening training (process-based training, n = 25), an implementation intention strategy training (strategy-based training, n = 23), or served as a non-contact control group (n = 30). Our results demonstrated that training participants improved their performance in the trained tasks (process-based training: d = 3.01, strategy-based training: d = 2.6). For untrained tasks, the process-based training group showed significant working memory (d = .58) as well as episodic memory task improvement (d = 1.19) compared to the strategy-based training and to the non-contact control group (all d &lt; .03). In contrast, in the strategy-based training group there was a tendency towards some performance gain in a fluid intelligence test (d = .92). These results indicate that cognitive training can be tailored to improve specific cognitive abilities.</t>
         </is>
       </c>
     </row>
     <row r="231" ht="80" customHeight="1">
-      <c r="A231" s="5" t="n">
+      <c r="A231" s="2" t="n">
         <v>1779</v>
       </c>
-      <c r="B231" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C231" s="5" t="n"/>
-      <c r="D231" s="6" t="n"/>
-      <c r="E231" s="7" t="inlineStr">
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>E2-非WM训练</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>商业认知训练程序(Lumosity等)，非WM训练</t>
+        </is>
+      </c>
+      <c r="E231" s="4" t="inlineStr">
         <is>
           <t>Online cognitive training in healthy older adults: a preliminary study on the effects of single versus multi-domain training.</t>
         </is>
       </c>
-      <c r="F231" s="6" t="inlineStr">
+      <c r="F231" s="3" t="inlineStr">
         <is>
           <t>Walton CC; Kavanagh A; Downey LA et al.</t>
         </is>
       </c>
-      <c r="G231" s="5" t="n">
+      <c r="G231" s="2" t="n">
         <v>2015</v>
       </c>
-      <c r="H231" s="6" t="inlineStr">
+      <c r="H231" s="3" t="inlineStr">
         <is>
           <t>Translational neuroscience</t>
         </is>
       </c>
-      <c r="I231" s="7" t="inlineStr">
+      <c r="I231" s="4" t="inlineStr">
         <is>
           <t>It has been argued that cognitive training may be effective in improving cognitive performance in healthy older adults. However, inappropriate active control groups often hinder the validity of these claims. Additionally there are relatively few independent empirical studies on popular commercially available cognitive training programs. The current research extends on previous work to explore cognitive training employing a more robust control group. Twenty-eight healthy older adults (age: M = 64.18, SD = 6.9) completed either a multi-faceted online computerised cognitive training program or trained on a simple reaction time task for 20 minutes a day over a 28 day period. Both groups significantly improved performance in multiple measures of processing speed. Only the treatment group displayed improved performance for measures of memory accuracy. These results suggest improvements in processing speed and visual working memory may be obtained over a short period of computerized cognitive training. However, gains over this time appear only to show near transfer. The use of similar active control groups in future research are needed in order to better understand changes in cognition after cognitive training.</t>
         </is>
@@ -10226,35 +10378,43 @@
       </c>
     </row>
     <row r="239" ht="80" customHeight="1">
-      <c r="A239" s="5" t="n">
+      <c r="A239" s="2" t="n">
         <v>1834</v>
       </c>
-      <c r="B239" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C239" s="5" t="n"/>
-      <c r="D239" s="6" t="n"/>
-      <c r="E239" s="7" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>E3-无认知结局</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>仅报告功能连接，无行为认知结局</t>
+        </is>
+      </c>
+      <c r="E239" s="4" t="inlineStr">
         <is>
           <t>Effects of Transcranial Direct Current Stimulation Paired With Cognitive Training on Functional Connectivity of the Working Memory Network in Older Adults.</t>
         </is>
       </c>
-      <c r="F239" s="6" t="inlineStr">
+      <c r="F239" s="3" t="inlineStr">
         <is>
           <t>Nissim NR; O'Shea A; Indahlastari A et al.</t>
         </is>
       </c>
-      <c r="G239" s="5" t="n">
+      <c r="G239" s="2" t="n">
         <v>2019</v>
       </c>
-      <c r="H239" s="6" t="inlineStr">
+      <c r="H239" s="3" t="inlineStr">
         <is>
           <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
-      <c r="I239" s="7" t="inlineStr">
+      <c r="I239" s="4" t="inlineStr">
         <is>
           <t>BACKGROUND: Working memory, a fundamental short-term cognitive process, is known to decline with advanced age even in healthy older adults. Normal age-related declines in working memory can cause loss of independence and decreased quality of life. Cognitive training has shown some potential at enhancing certain cognitive processes, although, enhancements are variable. Transcranial direct current stimulation (tDCS), a form of non-invasive brain stimulation, has shown promise at enhancing working memory abilities, and may further the benefits from cognitive training interventions. However, the neural mechanisms underlying tDCS brain-based enhancements remain unknown. OBJECTIVE/HYPOTHESIS: Assess the effects of a 2-week intervention of active-tDCS vs. sham paired with cognitive training on functional connectivity of the working memory network during an N-Back working memory task. METHODS: Healthy older adults (N = 28; mean age = 74 ± 7.3) completed 10-sessions of cognitive training paired with active or sham-tDCS. Functional connectivity was evaluated at baseline and post-intervention during an N-Back task (2-Back vs. 0-Back). RESULTS: Active-tDCS vs. sham demonstrated a significant increase in connectivity between the left dorsolateral prefrontal cortex and right inferior parietal lobule at post-intervention during 2-Back. Target accuracy on 2-Back was significantly improved for active vs. sham at post-intervention. CONCLUSION: These results suggest pairing tDCS with cognitive training enhances functional connectivity and working memory performance in older adults, and thus may hold promise as a method for remediating age-related cognitive decline. Future studies evaluating optimal dose and long-term effects of tDCS on brain function will help to maximize potential clinical impacts of tDCS paired with cognitive training in older adults. CLINICAL TRIAL REGISTRATION: www.ClinicalTrials.gov, identifier NCT02137122.</t>
         </is>
@@ -10538,35 +10698,43 @@
       </c>
     </row>
     <row r="247" ht="80" customHeight="1">
-      <c r="A247" s="5" t="n">
+      <c r="A247" s="2" t="n">
         <v>1873</v>
       </c>
-      <c r="B247" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C247" s="5" t="n"/>
-      <c r="D247" s="6" t="n"/>
-      <c r="E247" s="7" t="inlineStr">
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>E1-非老年人群</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>含主观认知下降(SCD)患者，非健康老年人</t>
+        </is>
+      </c>
+      <c r="E247" s="4" t="inlineStr">
         <is>
           <t>Efficacy of Cognitive Training in Older Adults with and without Subjective Cognitive Decline Is Associated with Inhibition Efficiency and Working Memory Span, Not with Cognitive Reserve.</t>
         </is>
       </c>
-      <c r="F247" s="6" t="inlineStr">
+      <c r="F247" s="3" t="inlineStr">
         <is>
           <t>López-Higes R; Martín-Aragoneses MT; Rubio-Valdehita S et al.</t>
         </is>
       </c>
-      <c r="G247" s="5" t="n">
+      <c r="G247" s="2" t="n">
         <v>2018</v>
       </c>
-      <c r="H247" s="6" t="inlineStr">
+      <c r="H247" s="3" t="inlineStr">
         <is>
           <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
-      <c r="I247" s="7" t="inlineStr">
+      <c r="I247" s="4" t="inlineStr">
         <is>
           <t>The present study explores the role of cognitive reserve, executive functions, and working memory (WM) span, as factors that might explain training outcomes in cognitive status. Eighty-one older adults voluntarily participated in the study, classified either as older adults with subjective cognitive decline or cognitively intact. Each participant underwent a neuropsychological assessment that was conducted both at baseline (entailing cognitive reserve, executive functions, WM span and depressive symptomatology measures, as well as the Mini-Mental State Exam regarding initial cognitive status), and then 6 months later, once each participant had completed the training program (Mini-Mental State Exam at the endpoint). With respect to cognitive status the training program was most beneficial for subjective cognitive decline participants with low efficiency in inhibition at baseline (explaining a 33% of Mini-Mental State Exam total variance), whereas for cognitively intact participants training gains were observed for those who presented lower WM span.</t>
         </is>
@@ -13250,35 +13418,43 @@
       </c>
     </row>
     <row r="311" ht="80" customHeight="1">
-      <c r="A311" s="5" t="n">
+      <c r="A311" s="2" t="n">
         <v>2485</v>
       </c>
-      <c r="B311" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C311" s="5" t="n"/>
-      <c r="D311" s="6" t="n"/>
-      <c r="E311" s="7" t="inlineStr">
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>E3-无认知结局</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="inlineStr">
+        <is>
+          <t>仅报告眼动预测指标，无训练干预</t>
+        </is>
+      </c>
+      <c r="E311" s="4" t="inlineStr">
         <is>
           <t>Spontaneous eye blinks predict executive functioning in seniors</t>
         </is>
       </c>
-      <c r="F311" s="6" t="inlineStr">
+      <c r="F311" s="3" t="inlineStr">
         <is>
           <t>Buitenweg, Jessika I. V.; Murre, Jaap M. J.; Ridderinkhof, K. Richard</t>
         </is>
       </c>
-      <c r="G311" s="5" t="n">
+      <c r="G311" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="H311" s="6" t="inlineStr">
+      <c r="H311" s="3" t="inlineStr">
         <is>
           <t>Journal of Cognitive Enhancement</t>
         </is>
       </c>
-      <c r="I311" s="7" t="inlineStr">
+      <c r="I311" s="4" t="inlineStr">
         <is>
           <t>As the world’s population is aging rapidly, cognitive training is an extensively used approach to attempt improvement of age-related cognitive functioning. With increasing numbers of older adults required to remain in the workforce, it is important to be able to reliably predict future functional decline, as well as the individual advantages of cognitive training. Given the correlation between age-related decline and striatal dopaminergic function, we investigated whether eye blink rate (EBR), a non-invasive, indirect indicator of dopaminergic activity, could predict executive functioning (response inhibition, switching and working memory updating) as well as trainability of executive functioning in older adults. EBR was collected before and after a cognitive flexibility training, cognitive training without flexibility, or a mock training. EBR predicted working memory updating performance on two measures of updating, as well as trainability of working memory updating, whereas performance and trainability in inhibition and switching tasks could not be predicted by EBR. Our findings tentatively indicate that EBR permits prediction of working memory performance in older adults. To fully interpret the relationship with executive functioning, we suggest future research should assess both EBR and dopamine receptor availability among seniors. (PsycInfo Database Record (c) 2023 APA, all rights reserved)</t>
         </is>
@@ -14129,43 +14305,43 @@
       </c>
     </row>
     <row r="332" ht="80" customHeight="1">
-      <c r="A332" s="5" t="n">
+      <c r="A332" s="2" t="n">
         <v>2538</v>
       </c>
-      <c r="B332" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C332" s="5" t="inlineStr">
-        <is>
-          <t>年龄范围57-73岁</t>
-        </is>
-      </c>
-      <c r="D332" s="6" t="inlineStr">
-        <is>
-          <t>同#56重复报告，年龄57-73岁，纳入备注重复</t>
-        </is>
-      </c>
-      <c r="E332" s="7" t="inlineStr">
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>E8-重复报告</t>
+        </is>
+      </c>
+      <c r="D332" s="3" t="inlineStr">
+        <is>
+          <t>与#56重复，同一研究</t>
+        </is>
+      </c>
+      <c r="E332" s="4" t="inlineStr">
         <is>
           <t>Age-specific differences of dualn-back training</t>
         </is>
       </c>
-      <c r="F332" s="6" t="inlineStr">
+      <c r="F332" s="3" t="inlineStr">
         <is>
           <t>Salminen, Tiina; Frensch, Peter; Strobach, Tilo et al.</t>
         </is>
       </c>
-      <c r="G332" s="5" t="n">
+      <c r="G332" s="2" t="n">
         <v>2016</v>
       </c>
-      <c r="H332" s="6" t="inlineStr">
+      <c r="H332" s="3" t="inlineStr">
         <is>
           <t>Aging, Neuropsychology, and Cognition</t>
         </is>
       </c>
-      <c r="I332" s="7" t="inlineStr">
+      <c r="I332" s="4" t="inlineStr">
         <is>
           <t>Age-related decline in executive functions can be decisive in performing everyday tasks autonomously. Working memory (WM) is closely related to executive functions, and training of WM has yielded evidence toward cognitive plasticity in older adults. The training effects often transfer to untrained tasks and functions. These effects have mostly been shown in processes such as WM and attention, whereas studies investigating transfer to executive functions have been scarce. We trained older adults aged 57–73 years in a WM training task that was reported to be effective in producing transfer in young adults. The training intervention consisted of a dual n-back task including independently processed auditory and visual n-back tasks. We investigated transfer to tasks engaging executive functions, and compared the effects in older adults to those reported in young adults. We found that both training groups improved in the training task. Although the training effect in older adults was smaller than the training effect in young adults, the older adults still showed a notable improvement so that after training they performed on the same level as young adults without training. The older adults also showed transfer to an untrained WM updating task, a result that was in accordance with the findings in young adults; other transfer effects in older adults were lacking. We conclude that although transfer effects were scarce, the present study provides encouraging evidence toward the possibilities to compensate for age-related decline in executive functions by a WM training intervention. (PsycInfo Database Record (c) 2024 APA, all rights reserved)</t>
         </is>
@@ -14465,35 +14641,43 @@
       </c>
     </row>
     <row r="340" ht="80" customHeight="1">
-      <c r="A340" s="5" t="n">
+      <c r="A340" s="2" t="n">
         <v>2561</v>
       </c>
-      <c r="B340" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C340" s="5" t="n"/>
-      <c r="D340" s="6" t="n"/>
-      <c r="E340" s="7" t="inlineStr">
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>E2-非WM训练</t>
+        </is>
+      </c>
+      <c r="D340" s="3" t="inlineStr">
+        <is>
+          <t>处理速度在线训练，非WM训练</t>
+        </is>
+      </c>
+      <c r="E340" s="4" t="inlineStr">
         <is>
           <t>Improved processing speed: Online computer-based cognitive training in older adults</t>
         </is>
       </c>
-      <c r="F340" s="6" t="inlineStr">
+      <c r="F340" s="3" t="inlineStr">
         <is>
           <t>Simpson, Tamara; Camfield, David; Pipingas, Andrew et al.</t>
         </is>
       </c>
-      <c r="G340" s="5" t="n">
+      <c r="G340" s="2" t="n">
         <v>2012</v>
       </c>
-      <c r="H340" s="6" t="inlineStr">
+      <c r="H340" s="3" t="inlineStr">
         <is>
           <t>Educational Gerontology</t>
         </is>
       </c>
-      <c r="I340" s="7" t="inlineStr">
+      <c r="I340" s="4" t="inlineStr">
         <is>
           <t>In an increasingly aging population, a number of adults are concerned about declines in their cognitive abilities. Online computer-based cognitive training programs have been proposed as an accessible means by which the elderly may improve their cognitive abilities; yet, more research is needed in order to assess the efficacy of these programs. In the current study, a commercially available 21-day online computer-based cognitive training intervention was administered to 34 individuals aged between 53 and 75 years. The intervention consisted of computerized training in reaction time, inspection time, short-term memory for words, executive function, visual spatial acuity, arithmetic, visual spatial memory, visual scanning=discrimination, and n-back working memory. An active solitaire control group was also included. Participants were tested at baseline, posttraining and at three-weeks follow-up using a battery of neuropsychological outcome measures. These consisted of simple reaction time, complex reaction time, digit forwards and backwards, spatial working memory, digit symbol substitution, RAVLT, and trail making. Significant improvement in simple reaction time and choice reaction time task was found in the cognitive training group both posttraining and at three-weeks follow-up. However, no significant improvements on the other cognitive tasks were found. The training program was found to be successful in achieving transfer of trained cognitive abilities in speed of processing to similar untrained tasks. (PsycInfo Database Record (c) 2024 APA, all rights reserved)</t>
         </is>
@@ -16677,35 +16861,43 @@
       </c>
     </row>
     <row r="392" ht="80" customHeight="1">
-      <c r="A392" s="5" t="n">
+      <c r="A392" s="2" t="n">
         <v>2792</v>
       </c>
-      <c r="B392" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C392" s="5" t="n"/>
-      <c r="D392" s="6" t="n"/>
-      <c r="E392" s="7" t="inlineStr">
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>E1-非老年人群</t>
+        </is>
+      </c>
+      <c r="D392" s="3" t="inlineStr">
+        <is>
+          <t>年轻成人为主，无老年组</t>
+        </is>
+      </c>
+      <c r="E392" s="4" t="inlineStr">
         <is>
           <t>Expectation effects in working memory training</t>
         </is>
       </c>
-      <c r="F392" s="6" t="inlineStr">
+      <c r="F392" s="3" t="inlineStr">
         <is>
           <t>Parong, Jocelyn and Seitz, Aaron R. and Jaeggi, Susanne M. and Green, C.    Shawn</t>
         </is>
       </c>
-      <c r="G392" s="5" t="n">
+      <c r="G392" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="H392" s="6" t="inlineStr">
+      <c r="H392" s="3" t="inlineStr">
         <is>
           <t>PROCEEDINGS OF THE NATIONAL ACADEMY OF SCIENCES OF THE UNITED STATES OF    AMERICA</t>
         </is>
       </c>
-      <c r="I392" s="7" t="inlineStr">
+      <c r="I392" s="4" t="inlineStr">
         <is>
           <t>There is a growing body of research focused on developing and evaluating    behavioral training paradigms meant to induce enhancements in cognitive    function. It has recently been proposed that one mechanism through which    such performance gains could be induced involves participants'    expectations of improvement. However, no work to date has evaluated    whether it is possible to cause changes in cognitive function in a    longterm behavioral training study by manipulating expectations. In this    study, positive or negative expectations about cognitive training were    both explicitly and associatively induced before either a working memory    training intervention or a control intervention. Consistent with    previous work, a main effect of the training condition was found, with    individuals trained on the working memory task showing larger gains in    cognitive function than those trained on the control task.    Interestingly, a main effect of expectation was also found, with    individuals given positive expectations showing larger cognitive gains    than those who were given negative expectations (regardless of training    condition). No interaction effect between training and expectations was    found. Exploratory analyses suggest that certain individual    characteristics (e.g., personality, motivation) moderate the size of the    expectation effect. These results highlight aspects of methodology that    can inform future behavioral interventions and suggest that participant    expectations could be capitalized on to maximize training outcomes.</t>
         </is>
@@ -17728,35 +17920,43 @@
       </c>
     </row>
     <row r="417" ht="80" customHeight="1">
-      <c r="A417" s="5" t="n">
+      <c r="A417" s="2" t="n">
         <v>2872</v>
       </c>
-      <c r="B417" s="5" t="inlineStr">
-        <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="C417" s="5" t="n"/>
-      <c r="D417" s="6" t="n"/>
-      <c r="E417" s="7" t="inlineStr">
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>E1-非老年人群</t>
+        </is>
+      </c>
+      <c r="D417" s="3" t="inlineStr">
+        <is>
+          <t>混合年龄样本，无单独老年数据</t>
+        </is>
+      </c>
+      <c r="E417" s="4" t="inlineStr">
         <is>
           <t>The role of strategy use in working memory training outcomes</t>
         </is>
       </c>
-      <c r="F417" s="6" t="inlineStr">
+      <c r="F417" s="3" t="inlineStr">
         <is>
           <t>Fellman, Daniel and Jylkka, Jussi and Waris, Otto and Soveri, Anna and    Ritakallio, Liisa and Haga, Sarah and Salmi, Juha and Nyman, Thomas J.    and Laine, Matti</t>
         </is>
       </c>
-      <c r="G417" s="5" t="n">
+      <c r="G417" s="2" t="n">
         <v>2020</v>
       </c>
-      <c r="H417" s="6" t="inlineStr">
+      <c r="H417" s="3" t="inlineStr">
         <is>
           <t>JOURNAL OF MEMORY AND LANGUAGE</t>
         </is>
       </c>
-      <c r="I417" s="7" t="inlineStr">
+      <c r="I417" s="4" t="inlineStr">
         <is>
           <t>Cognitive mechanisms underlying the limited transfer effects of working    memory (WM) training remain poorly understood. We tested in detail the    Strategy Mediation hypothesis, according to which WM training generates    task-specific strategies that facilitate performance on the trained task    and its untrained variants. This large-scale pre-registered randomized    controlled trial (n = 258) used a 4-week adaptive WM training with a    single digit n-back task. Strategy use was probed with open-ended    strategy reports. We employed a Strategy training group (n = 73)    receiving external strategy instruction, a Traditional training group (n    = 118) practicing without strategy instruction, and Passive controls (n    = 67). Both training groups showed emerging transfer to untrained n-back    task variants already at intermediate test after 3 training sessions,    extending to all untrained n-back task variants at posttest after 12    training sessions. The Strategy training group outperformed the    Traditional training group only at the beginning of training, indicating    short-lived strategy manipulation effects. Importantly, in the    Traditional training group, strategy evolvement modulated the gains in    the trained and untrained n -back tasks, supporting the Strategy    Mediation hypothesis. Our results concur with the view of WM training as    cognitive skill learning.</t>
         </is>
